--- a/doc/checkers-inventory/eProcurement conceptual model checkers inventory.xlsx
+++ b/doc/checkers-inventory/eProcurement conceptual model checkers inventory.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$7:$H$68</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$7:$H$74</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="209">
   <si>
     <t xml:space="preserve">Inventory of checkers for the UML model conventions</t>
   </si>
@@ -55,6 +55,9 @@
     <t xml:space="preserve">pseudo code</t>
   </si>
   <si>
+    <t xml:space="preserve">comment</t>
+  </si>
+  <si>
     <t xml:space="preserve">association</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
   </si>
   <si>
     <t xml:space="preserve">check the connector source role is provided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this should be deprecated</t>
   </si>
   <si>
     <t xml:space="preserve">multiplicity</t>
@@ -139,6 +145,9 @@
     <t xml:space="preserve">check if class has at least one attribute</t>
   </si>
   <si>
+    <t xml:space="preserve">should we still keep this as a recommendation?</t>
+  </si>
+  <si>
     <t xml:space="preserve">connectors</t>
   </si>
   <si>
@@ -208,6 +217,9 @@
     <t xml:space="preserve">check that datatype is legal, i.e. in the list of permitted types or enumeration</t>
   </si>
   <si>
+    <t xml:space="preserve">do we still permit UML common types?</t>
+  </si>
+  <si>
     <t xml:space="preserve">discouraged UML datatype</t>
   </si>
   <si>
@@ -217,6 +229,9 @@
     <t xml:space="preserve">check if datatype is UML</t>
   </si>
   <si>
+    <t xml:space="preserve">we switched to xsd. Not needed anymore.</t>
+  </si>
+  <si>
     <t xml:space="preserve">undefined type</t>
   </si>
   <si>
@@ -226,6 +241,9 @@
     <t xml:space="preserve">check if an element (class, enumeration or datatype) exists with the name $attributeType$</t>
   </si>
   <si>
+    <t xml:space="preserve">?</t>
+  </si>
+  <si>
     <t xml:space="preserve">counter-part</t>
   </si>
   <si>
@@ -238,6 +256,9 @@
     <t xml:space="preserve">check if there is a dependecy relation with the same name and source class</t>
   </si>
   <si>
+    <t xml:space="preserve">we don t have Code type attributes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">class-attribute-&gt;common</t>
   </si>
   <si>
@@ -328,7 +349,7 @@
     <t xml:space="preserve">stereotype provided</t>
   </si>
   <si>
-    <t xml:space="preserve">The $stereotypeName$ stareotype is applied to $elementName$. Stereotypes are discouraged in the current practice with some exceptions. </t>
+    <t xml:space="preserve">The $stereotypeName$ stereotype is applied to $elementName$. Stereotypes are discouraged in the current practice with some exceptions. </t>
   </si>
   <si>
     <t xml:space="preserve">check if element has stereotype and if it is in the set of exceptions</t>
@@ -476,6 +497,9 @@
   </si>
   <si>
     <t xml:space="preserve">select the target name of the generalisation connector; then count how many generalisations have the same target; they must be 2 or more.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not sure about this one. For example foaf:Person has only one child, cpv:Person</t>
   </si>
   <si>
     <t xml:space="preserve">inverse inheritance</t>
@@ -521,6 +545,9 @@
             Destination </t>
   </si>
   <si>
+    <t xml:space="preserve">how is this checked?</t>
+  </si>
+  <si>
     <t xml:space="preserve">package</t>
   </si>
   <si>
@@ -533,10 +560,13 @@
     <t xml:space="preserve">check if name matches regex [a-zA-Z0-9]+</t>
   </si>
   <si>
+    <t xml:space="preserve">should we permit spaces in packages?</t>
+  </si>
+  <si>
     <t xml:space="preserve">The package name is missing. Packages must be named.  </t>
   </si>
   <si>
-    <t xml:space="preserve">chekc if name value is empty or missing</t>
+    <t xml:space="preserve">check if name value is empty or missing</t>
   </si>
   <si>
     <t xml:space="preserve">owned elements</t>
@@ -898,6 +928,37 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1C232"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE599"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF3D3D3D"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -971,7 +1032,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA1048576"/>
-  <sheetFormatPr defaultColWidth="14.4453125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.4609375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.71"/>
@@ -981,6 +1042,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="43.07"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1070,7 +1132,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -1096,1568 +1158,1598 @@
         <f aca="false">CONCATENATE("counter (", MAX(H8:H177),")")</f>
         <v>counter (73)</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I7" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="str">
         <f aca="false">CONCATENATE(B8,"-",C8,"-",H8)</f>
         <v>association-source-30</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="str">
         <f aca="false">CONCATENATE(B9,"-",C9,"-",H9)</f>
         <v>association-multiplicity-33</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="str">
         <f aca="false">CONCATENATE(B10,"-",C10,"-",H10)</f>
         <v>association-multiplicity-35</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="str">
         <f aca="false">CONCATENATE(B11,"-",C11,"-",H11)</f>
         <v>association-&gt;connector-inherits all from checkers in category connector-36</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="str">
         <f aca="false">CONCATENATE(B12,"-",C12,"-",H12)</f>
         <v>class-name-14</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="str">
         <f aca="false">CONCATENATE(B13,"-",C13,"-",H13)</f>
         <v>class-attributes-15</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="0" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="str">
         <f aca="false">CONCATENATE(B14,"-",C14,"-",H14)</f>
         <v>class-connectors-16</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="str">
         <f aca="false">CONCATENATE(B15,"-",C15,"-",H15)</f>
         <v>class-&gt;common-name-11</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="str">
         <f aca="false">CONCATENATE(B16,"-",C16,"-",H16)</f>
         <v>class-&gt;common-description-12</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="str">
         <f aca="false">CONCATENATE(B17,"-",C17,"-",H17)</f>
         <v>class-&gt;common-stereotype-13</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="str">
         <f aca="false">CONCATENATE(B18,"-",C18,"-",H18)</f>
         <v>class-attribute-name-21</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="str">
         <f aca="false">CONCATENATE(B19,"-",C19,"-",H19)</f>
         <v>class-attribute-multiplicity-22</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="str">
         <f aca="false">CONCATENATE(B20,"-",C20,"-",H20)</f>
         <v>class-attribute-type-23</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="str">
         <f aca="false">CONCATENATE(B21,"-",C21,"-",H21)</f>
         <v>class-attribute-type-24</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="str">
         <f aca="false">CONCATENATE(B22,"-",C22,"-",H22)</f>
         <v>class-attribute-type-25</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="0" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="str">
         <f aca="false">CONCATENATE(B23,"-",C23,"-",H23)</f>
         <v>class-attribute-counter-part-65</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>65</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="str">
         <f aca="false">CONCATENATE(B24,"-",C24,"-",H24)</f>
         <v>class-attribute-&gt;common-name-18</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="str">
         <f aca="false">CONCATENATE(B25,"-",C25,"-",H25)</f>
         <v>class-attribute-&gt;common-description-19</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="str">
         <f aca="false">CONCATENATE(B26,"-",C26,"-",H26)</f>
         <v>class-attribute-&gt;common-stereotype-20</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="str">
         <f aca="false">CONCATENATE(B27,"-",C27,"-",H27)</f>
         <v>common-name-1</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="str">
         <f aca="false">CONCATENATE(B28,"-",C28,"-",H28)</f>
         <v>common-name-2</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="str">
         <f aca="false">CONCATENATE(B29,"-",C29,"-",H29)</f>
         <v>common-name-3</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="str">
         <f aca="false">CONCATENATE(B30,"-",C30,"-",H30)</f>
         <v>common-name-4</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="str">
         <f aca="false">CONCATENATE(B31,"-",C31,"-",H31)</f>
         <v>common-name-5</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="str">
         <f aca="false">CONCATENATE(B32,"-",C32,"-",H32)</f>
         <v>common-name-6</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="str">
         <f aca="false">CONCATENATE(B33,"-",C33,"-",H33)</f>
         <v>common-name-7</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="str">
         <f aca="false">CONCATENATE(B34,"-",C34,"-",H34)</f>
         <v>common-name-8</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="str">
         <f aca="false">CONCATENATE(B35,"-",C35,"-",H35)</f>
         <v>common-description-9</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="str">
         <f aca="false">CONCATENATE(B36,"-",C36,"-",H36)</f>
         <v>common-stereotype-10</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="str">
         <f aca="false">CONCATENATE(B37,"-",C37,"-",H37)</f>
         <v>common-name-57</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="str">
         <f aca="false">CONCATENATE(B38,"-",C38,"-",H38)</f>
         <v>common-name-58</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="str">
         <f aca="false">CONCATENATE(B39,"-",C39,"-",H39)</f>
         <v>connector-name-27</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="str">
         <f aca="false">CONCATENATE(B40,"-",C40,"-",H40)</f>
         <v>connector-description-28</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="str">
         <f aca="false">CONCATENATE(B41,"-",C41,"-",H41)</f>
         <v>connector-target-29</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="str">
         <f aca="false">CONCATENATE(B42,"-",C42,"-",H42)</f>
         <v>connector-direction-31</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="str">
         <f aca="false">CONCATENATE(B43,"-",C43,"-",H43)</f>
         <v>connector-multiplicity-32</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="str">
         <f aca="false">CONCATENATE(B44,"-",C44,"-",H44)</f>
         <v>connector-multiplicity-34</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="str">
         <f aca="false">CONCATENATE(B45,"-",C45,"-",H45)</f>
         <v>connector-direction-63</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="str">
         <f aca="false">CONCATENATE(B46,"-",C46,"-",H46)</f>
         <v>datatype-name-61</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="str">
         <f aca="false">CONCATENATE(B47,"-",C47,"-",H47)</f>
         <v>datatype-&gt;common-name-54</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="str">
         <f aca="false">CONCATENATE(B48,"-",C48,"-",H48)</f>
         <v>datatype-&gt;common-description-55</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="str">
         <f aca="false">CONCATENATE(B49,"-",C49,"-",H49)</f>
         <v>datatype-&gt;common-stereotype-56</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="str">
         <f aca="false">CONCATENATE(B50,"-",C50,"-",H50)</f>
         <v>dependency-direction-64</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="str">
         <f aca="false">CONCATENATE(B51,"-",C51,"-",H51)</f>
         <v>dependency-&gt;connector-inherits all from checkers in category connector-37</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="str">
         <f aca="false">CONCATENATE(B52,"-",C52,"-",H52)</f>
         <v>enumeration-name-59</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>59</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="str">
         <f aca="false">CONCATENATE(B53,"-",C53,"-",H53)</f>
         <v>enumeration-&gt;common-name-48</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H53" s="15" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="str">
         <f aca="false">CONCATENATE(B54,"-",C54,"-",H54)</f>
         <v>enumeration-&gt;common-stereotype-49</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="str">
         <f aca="false">CONCATENATE(B55,"-",C55,"-",H55)</f>
         <v>enumeration-&gt;common-description-50</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="str">
         <f aca="false">CONCATENATE(B56,"-",C56,"-",H56)</f>
         <v>generalisation-hierarchy-38</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>38</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I56" s="0" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="str">
         <f aca="false">CONCATENATE(B57,"-",C57,"-",H57)</f>
         <v>generalisation-hierarchy-39</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="str">
         <f aca="false">CONCATENATE(B58,"-",C58,"-",H58)</f>
         <v>generalisation-multiplicity-40</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="str">
         <f aca="false">CONCATENATE(B59,"-",C59,"-",H59)</f>
         <v>generalisation-name-41</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H59" s="15" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="str">
         <f aca="false">CONCATENATE(B60,"-",C60,"-",H60)</f>
         <v>generalisation-name-42</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="str">
         <f aca="false">CONCATENATE(B61,"-",C61,"-",H61)</f>
         <v>generalisation-direction-62</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>62</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I61" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="str">
         <f aca="false">CONCATENATE(B62,"-",C62,"-",H62)</f>
         <v>package-name-43</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H62" s="12" t="n">
         <v>43</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I62" s="0" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="str">
         <f aca="false">CONCATENATE(B63,"-",C63,"-",H63)</f>
         <v>package-name-46</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="str">
         <f aca="false">CONCATENATE(B64,"-",C64,"-",H64)</f>
         <v>package-owned elements-47</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>47</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="str">
         <f aca="false">CONCATENATE(B65,"-",C65,"-",H65)</f>
         <v>package-&gt;common-description-44</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H65" s="15" t="n">
         <v>44</v>
@@ -2682,28 +2774,28 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="str">
         <f aca="false">CONCATENATE(B66,"-",C66,"-",H66)</f>
         <v>package-&gt;common-stereotype-45</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>45</v>
@@ -2728,217 +2820,217 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="str">
         <f aca="false">CONCATENATE(B67,"-",C67,"-",H67)</f>
         <v>class-attribute-type-66</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F67" s="18" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="H67" s="15" t="n">
         <v>66</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="str">
         <f aca="false">CONCATENATE(B68,"-",C68,"-",H68)</f>
         <v>class-name-67</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H68" s="21" t="n">
         <v>67</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="13" t="str">
         <f aca="false">CONCATENATE(B69,"-",C69,"-",H69)</f>
         <v>connectors-with-same-name-multiplicity-68</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="F69" s="18" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H69" s="22" t="n">
         <v>68</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="str">
         <f aca="false">CONCATENATE(B70,"-",C70,"-",H70)</f>
         <v>connectors-with-same-name-definition-69</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H70" s="21" t="n">
         <v>69</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="str">
         <f aca="false">CONCATENATE(B71,"-",C71,"-",H71)</f>
         <v>connectors-with-same-name-definition-70</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F71" s="18" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H71" s="22" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="str">
         <f aca="false">CONCATENATE(B72,"-",C72,"-",H72)</f>
         <v>class-attributes-with-same-name-definition-71</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G72" s="20" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="H72" s="21" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="13" t="str">
         <f aca="false">CONCATENATE(B73,"-",C73,"-",H73)</f>
         <v>class-attributes-with-same-name-multiplicity-72</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E73" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="F73" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="F73" s="18" t="s">
-        <v>183</v>
-      </c>
       <c r="G73" s="18" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H73" s="22" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="str">
         <f aca="false">CONCATENATE(B74,"-",C74,"-",H74)</f>
         <v>class-attributes-with-same-name-data-types-73</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="G74" s="20" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="H74" s="21" t="n">
         <v>73</v>
@@ -12199,15 +12291,15 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A7:H68"/>
+  <autoFilter ref="A7:H74"/>
   <mergeCells count="3">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A5:F5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/doc/checkers-inventory/eProcurement conceptual model checkers inventory.xlsx
+++ b/doc/checkers-inventory/eProcurement conceptual model checkers inventory.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$7:$H$74</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$7:$H$76</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="221">
   <si>
     <t xml:space="preserve">Inventory of checkers for the UML model conventions</t>
   </si>
@@ -76,7 +76,7 @@
     <t xml:space="preserve">check the connector source role is provided</t>
   </si>
   <si>
-    <t xml:space="preserve">this should be deprecated</t>
+    <t xml:space="preserve">delete this rule</t>
   </si>
   <si>
     <t xml:space="preserve">multiplicity</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">name</t>
   </si>
   <si>
-    <t xml:space="preserve">class is not PascalNamed</t>
+    <t xml:space="preserve">class is not PascalCased</t>
   </si>
   <si>
     <t xml:space="preserve">The class name $value$ is invalid. The class name must start with a capital case.</t>
@@ -136,6 +136,9 @@
     <t xml:space="preserve">attributes</t>
   </si>
   <si>
+    <t xml:space="preserve">info</t>
+  </si>
+  <si>
     <t xml:space="preserve">underspecified class</t>
   </si>
   <si>
@@ -145,7 +148,7 @@
     <t xml:space="preserve">check if class has at least one attribute</t>
   </si>
   <si>
-    <t xml:space="preserve">should we still keep this as a recommendation?</t>
+    <t xml:space="preserve">This should be an info</t>
   </si>
   <si>
     <t xml:space="preserve">connectors</t>
@@ -211,13 +214,41 @@
     <t xml:space="preserve">invalid datatype</t>
   </si>
   <si>
-    <t xml:space="preserve">The attribute type $attributeType$ is invalid. Attributes must use datatypes that are either: (a) UML common types, (b) XSD or RDF datatypes (c) custom datatype or (d) enumeration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">check that datatype is legal, i.e. in the list of permitted types or enumeration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">do we still permit UML common types?</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The attribute type $attributeType$ is invalid. Attributes must use datatypes that are either: (a) XSD or RDF datatypes or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">(b)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> belonging to a shortlist of custom URIs (datatypes or classes).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">check that datatype is legal, i.e. in the list of permitted standard or custom datatypes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text in column F &amp; G changed. Implement accordingly</t>
   </si>
   <si>
     <t xml:space="preserve">discouraged UML datatype</t>
@@ -229,9 +260,6 @@
     <t xml:space="preserve">check if datatype is UML</t>
   </si>
   <si>
-    <t xml:space="preserve">we switched to xsd. Not needed anymore.</t>
-  </si>
-  <si>
     <t xml:space="preserve">undefined type</t>
   </si>
   <si>
@@ -241,7 +269,7 @@
     <t xml:space="preserve">check if an element (class, enumeration or datatype) exists with the name $attributeType$</t>
   </si>
   <si>
-    <t xml:space="preserve">?</t>
+    <t xml:space="preserve">delete this rule. (after that delete the datatype package from each module in ePO_CM.eap file)</t>
   </si>
   <si>
     <t xml:space="preserve">counter-part</t>
@@ -256,7 +284,7 @@
     <t xml:space="preserve">check if there is a dependecy relation with the same name and source class</t>
   </si>
   <si>
-    <t xml:space="preserve">we don t have Code type attributes.</t>
+    <t xml:space="preserve">delete this rule.</t>
   </si>
   <si>
     <t xml:space="preserve">class-attribute-&gt;common</t>
@@ -328,6 +356,9 @@
     <t xml:space="preserve">check if local segment contains delimiters (spaces) regex [\s]+</t>
   </si>
   <si>
+    <t xml:space="preserve">modified severity to error (column D)</t>
+  </si>
+  <si>
     <t xml:space="preserve">names must be unique</t>
   </si>
   <si>
@@ -337,6 +368,9 @@
     <t xml:space="preserve">check that (a) for elements: no other elements or connectors; (b) for attributes: no other elements; (c) for connectors: no other elements ... have the same name</t>
   </si>
   <si>
+    <t xml:space="preserve">this rule applies only to classes, enumerations, datatypes and instances (boxes). This rule does not apply to connectors and attributes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">missing description</t>
   </si>
   <si>
@@ -373,6 +407,36 @@
     <t xml:space="preserve">check if it is a valid Qname- XML</t>
   </si>
   <si>
+    <t xml:space="preserve">common-tag-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tag name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The tag $tagName$ of element $elementName$ must be an URI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check if tag name is a short URI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new rule to be implemented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">common-tag-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tag value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The tag $tagName$ of element $elementName$ must have a value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check if tag has a value.</t>
+  </si>
+  <si>
     <t xml:space="preserve">connector</t>
   </si>
   <si>
@@ -409,7 +473,7 @@
     <t xml:space="preserve">invalid relationship direction</t>
   </si>
   <si>
-    <t xml:space="preserve">The connector $connectorName$ employ invalid direction $direction$. Connectors must employ "Sourge-&gt;Destination" or "Bidirectional" directions only. </t>
+    <t xml:space="preserve">The connector $connectorName$ employ invalid direction $direction$. Connectors must employ "Source-&gt;Destination" or "Bidirectional" directions only. </t>
   </si>
   <si>
     <t xml:space="preserve">check the connector direction is in the list ["src-&gt;dest", "bidir"]</t>
@@ -497,9 +561,6 @@
   </si>
   <si>
     <t xml:space="preserve">select the target name of the generalisation connector; then count how many generalisations have the same target; they must be 2 or more.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not sure about this one. For example foaf:Person has only one child, cpv:Person</t>
   </si>
   <si>
     <t xml:space="preserve">inverse inheritance</t>
@@ -545,9 +606,6 @@
             Destination </t>
   </si>
   <si>
-    <t xml:space="preserve">how is this checked?</t>
-  </si>
-  <si>
     <t xml:space="preserve">package</t>
   </si>
   <si>
@@ -560,7 +618,7 @@
     <t xml:space="preserve">check if name matches regex [a-zA-Z0-9]+</t>
   </si>
   <si>
-    <t xml:space="preserve">should we permit spaces in packages?</t>
+    <t xml:space="preserve">disable this rule.</t>
   </si>
   <si>
     <t xml:space="preserve">The package name is missing. Packages must be named.  </t>
@@ -582,9 +640,6 @@
   </si>
   <si>
     <t xml:space="preserve">package-&gt;common</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info</t>
   </si>
   <si>
     <t xml:space="preserve">date and time</t>
@@ -658,6 +713,15 @@
   </si>
   <si>
     <t xml:space="preserve">compare data-types for a group of class attributes with the same name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check for stereotypes indicating mandatory, optional and recommended elements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check for correct inheritance between connectors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check for relations to instances.</t>
   </si>
 </sst>
 </file>
@@ -669,7 +733,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -743,6 +807,18 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -826,7 +902,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -863,7 +939,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -897,6 +973,18 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1028,11 +1116,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA1048576"/>
-  <sheetFormatPr defaultColWidth="14.4609375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.48046875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.71"/>
@@ -1040,9 +1128,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="43.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="77.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1155,14 +1243,14 @@
         <v>9</v>
       </c>
       <c r="H7" s="9" t="str">
-        <f aca="false">CONCATENATE("counter (", MAX(H8:H177),")")</f>
+        <f aca="false">CONCATENATE("counter (", MAX(H8:H179),")")</f>
         <v>counter (73)</v>
       </c>
       <c r="I7" s="0" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="str">
         <f aca="false">CONCATENATE(B8,"-",C8,"-",H8)</f>
         <v>association-source-30</v>
@@ -1192,7 +1280,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="26.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="str">
         <f aca="false">CONCATENATE(B9,"-",C9,"-",H9)</f>
         <v>association-multiplicity-33</v>
@@ -1219,7 +1307,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="str">
         <f aca="false">CONCATENATE(B10,"-",C10,"-",H10)</f>
         <v>association-multiplicity-35</v>
@@ -1246,7 +1334,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="189.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="str">
         <f aca="false">CONCATENATE(B11,"-",C11,"-",H11)</f>
         <v>association-&gt;connector-inherits all from checkers in category connector-36</v>
@@ -1300,7 +1388,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="26.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="str">
         <f aca="false">CONCATENATE(B13,"-",C13,"-",H13)</f>
         <v>class-attributes-15</v>
@@ -1312,25 +1400,25 @@
         <v>34</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>15</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="str">
         <f aca="false">CONCATENATE(B14,"-",C14,"-",H14)</f>
         <v>class-connectors-16</v>
@@ -1339,19 +1427,19 @@
         <v>29</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>16</v>
@@ -1363,76 +1451,76 @@
         <v>class-&gt;common-name-11</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="16" t="s">
-        <v>44</v>
-      </c>
       <c r="G15" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="82.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="str">
         <f aca="false">CONCATENATE(B16,"-",C16,"-",H16)</f>
         <v>class-&gt;common-description-12</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E16" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>47</v>
-      </c>
       <c r="G16" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="82.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="str">
         <f aca="false">CONCATENATE(B17,"-",C17,"-",H17)</f>
         <v>class-&gt;common-stereotype-13</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="G17" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>13</v>
@@ -1444,7 +1532,7 @@
         <v>class-attribute-name-21</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>30</v>
@@ -1453,10 +1541,10 @@
         <v>13</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>33</v>
@@ -1465,13 +1553,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="str">
         <f aca="false">CONCATENATE(B19,"-",C19,"-",H19)</f>
         <v>class-attribute-multiplicity-22</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>18</v>
@@ -1480,88 +1568,88 @@
         <v>13</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="52.2" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="str">
         <f aca="false">CONCATENATE(B20,"-",C20,"-",H20)</f>
         <v>class-attribute-type-23</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="str">
         <f aca="false">CONCATENATE(B21,"-",C21,"-",H21)</f>
         <v>class-attribute-type-24</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>24</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="64.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="str">
         <f aca="false">CONCATENATE(B22,"-",C22,"-",H22)</f>
         <v>class-attribute-type-25</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>19</v>
@@ -1582,13 +1670,13 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="52.2" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="str">
         <f aca="false">CONCATENATE(B23,"-",C23,"-",H23)</f>
         <v>class-attribute-counter-part-65</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>71</v>
@@ -1624,22 +1712,22 @@
         <v>30</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E24" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>44</v>
-      </c>
       <c r="G24" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="82.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="str">
         <f aca="false">CONCATENATE(B25,"-",C25,"-",H25)</f>
         <v>class-attribute-&gt;common-description-19</v>
@@ -1648,25 +1736,25 @@
         <v>76</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="16" t="s">
-        <v>47</v>
-      </c>
       <c r="G25" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="82.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="str">
         <f aca="false">CONCATENATE(B26,"-",C26,"-",H26)</f>
         <v>class-attribute-&gt;common-stereotype-20</v>
@@ -1675,19 +1763,19 @@
         <v>76</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E26" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="17" t="s">
-        <v>50</v>
-      </c>
       <c r="G26" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>20</v>
@@ -1867,7 +1955,7 @@
         <v>30</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>96</v>
@@ -1880,6 +1968,9 @@
       </c>
       <c r="H33" s="15" t="n">
         <v>7</v>
+      </c>
+      <c r="I33" s="0" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1897,19 +1988,22 @@
         <v>13</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="0" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="26.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="str">
         <f aca="false">CONCATENATE(B35,"-",C35,"-",H35)</f>
         <v>common-description-9</v>
@@ -1918,25 +2012,25 @@
         <v>77</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="str">
         <f aca="false">CONCATENATE(B36,"-",C36,"-",H36)</f>
         <v>common-stereotype-10</v>
@@ -1945,19 +2039,19 @@
         <v>77</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>10</v>
@@ -1978,13 +2072,13 @@
         <v>13</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>57</v>
@@ -2005,652 +2099,647 @@
         <v>13</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="str">
-        <f aca="false">CONCATENATE(B39,"-",C39,"-",H39)</f>
-        <v>connector-name-27</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="14" t="s">
+    <row r="39" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="G39" s="14" t="s">
+      <c r="E39" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="H39" s="12"/>
+      <c r="I39" s="0" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="26.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="H39" s="15" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="str">
-        <f aca="false">CONCATENATE(B40,"-",C40,"-",H40)</f>
-        <v>connector-description-28</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="D40" s="11" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>118</v>
+        <v>123</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>124</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>125</v>
+      </c>
+      <c r="H40" s="12"/>
+      <c r="I40" s="0" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="str">
         <f aca="false">CONCATENATE(B41,"-",C41,"-",H41)</f>
-        <v>connector-target-29</v>
+        <v>connector-name-27</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="26.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="str">
         <f aca="false">CONCATENATE(B42,"-",C42,"-",H42)</f>
-        <v>connector-direction-31</v>
+        <v>connector-description-28</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="26.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="str">
         <f aca="false">CONCATENATE(B43,"-",C43,"-",H43)</f>
-        <v>connector-multiplicity-32</v>
+        <v>connector-target-29</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="str">
         <f aca="false">CONCATENATE(B44,"-",C44,"-",H44)</f>
-        <v>connector-multiplicity-34</v>
+        <v>connector-direction-31</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+      <c r="I44" s="20"/>
+    </row>
+    <row r="45" customFormat="false" ht="26.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="str">
         <f aca="false">CONCATENATE(B45,"-",C45,"-",H45)</f>
-        <v>connector-direction-63</v>
+        <v>connector-multiplicity-32</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="str">
         <f aca="false">CONCATENATE(B46,"-",C46,"-",H46)</f>
-        <v>datatype-name-61</v>
+        <v>connector-multiplicity-34</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="64.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="str">
         <f aca="false">CONCATENATE(B47,"-",C47,"-",H47)</f>
-        <v>datatype-&gt;common-name-54</v>
+        <v>connector-direction-63</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G47" s="16" t="s">
-        <v>44</v>
+        <v>136</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="str">
         <f aca="false">CONCATENATE(B48,"-",C48,"-",H48)</f>
-        <v>datatype-&gt;common-description-55</v>
+        <v>datatype-name-61</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="G48" s="17" t="s">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="str">
         <f aca="false">CONCATENATE(B49,"-",C49,"-",H49)</f>
-        <v>datatype-&gt;common-stereotype-56</v>
+        <v>datatype-&gt;common-name-54</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="82.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="str">
         <f aca="false">CONCATENATE(B50,"-",C50,"-",H50)</f>
-        <v>dependency-direction-64</v>
+        <v>datatype-&gt;common-description-55</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>145</v>
+        <v>47</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="82.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="str">
         <f aca="false">CONCATENATE(B51,"-",C51,"-",H51)</f>
-        <v>dependency-&gt;connector-inherits all from checkers in category connector-37</v>
+        <v>datatype-&gt;common-stereotype-56</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>27</v>
+        <v>152</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="26.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="str">
         <f aca="false">CONCATENATE(B52,"-",C52,"-",H52)</f>
-        <v>enumeration-name-59</v>
+        <v>dependency-direction-64</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>33</v>
+        <v>157</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="189.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="str">
         <f aca="false">CONCATENATE(B53,"-",C53,"-",H53)</f>
-        <v>enumeration-&gt;common-name-48</v>
+        <v>dependency-&gt;connector-inherits all from checkers in category connector-37</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>30</v>
+        <v>158</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>27</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="str">
         <f aca="false">CONCATENATE(B54,"-",C54,"-",H54)</f>
-        <v>enumeration-&gt;common-stereotype-49</v>
+        <v>enumeration-name-59</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G54" s="17" t="s">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="str">
         <f aca="false">CONCATENATE(B55,"-",C55,"-",H55)</f>
-        <v>enumeration-&gt;common-description-50</v>
+        <v>enumeration-&gt;common-name-48</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C55" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D55" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E55" s="16" t="s">
+      <c r="F55" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H55" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="F55" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="56" customFormat="false" ht="82.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="str">
         <f aca="false">CONCATENATE(B56,"-",C56,"-",H56)</f>
-        <v>generalisation-hierarchy-38</v>
+        <v>enumeration-&gt;common-stereotype-49</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E56" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="F56" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="G56" s="11" t="s">
-        <v>155</v>
+      <c r="F56" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="I56" s="0" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="82.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="str">
         <f aca="false">CONCATENATE(B57,"-",C57,"-",H57)</f>
-        <v>generalisation-hierarchy-39</v>
+        <v>enumeration-&gt;common-description-50</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="F57" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="G57" s="14" t="s">
-        <v>159</v>
+        <v>47</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="52.2" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="str">
         <f aca="false">CONCATENATE(B58,"-",C58,"-",H58)</f>
-        <v>generalisation-multiplicity-40</v>
+        <v>generalisation-hierarchy-38</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="64.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="str">
         <f aca="false">CONCATENATE(B59,"-",C59,"-",H59)</f>
-        <v>generalisation-name-41</v>
+        <v>generalisation-hierarchy-39</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="26.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="str">
         <f aca="false">CONCATENATE(B60,"-",C60,"-",H60)</f>
-        <v>generalisation-name-42</v>
+        <v>generalisation-multiplicity-40</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="str">
         <f aca="false">CONCATENATE(B61,"-",C61,"-",H61)</f>
-        <v>generalisation-direction-62</v>
+        <v>generalisation-name-41</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>124</v>
+        <v>30</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>125</v>
+        <v>174</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>62</v>
-      </c>
-      <c r="I61" s="0" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="str">
         <f aca="false">CONCATENATE(B62,"-",C62,"-",H62)</f>
-        <v>package-name-43</v>
+        <v>generalisation-name-42</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>30</v>
@@ -2659,402 +2748,440 @@
         <v>19</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="I62" s="0" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="str">
         <f aca="false">CONCATENATE(B63,"-",C63,"-",H63)</f>
-        <v>package-name-46</v>
+        <v>generalisation-direction-62</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="str">
         <f aca="false">CONCATENATE(B64,"-",C64,"-",H64)</f>
-        <v>package-owned elements-47</v>
+        <v>package-name-43</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>179</v>
+        <v>30</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>43</v>
+      </c>
+      <c r="I64" s="0" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="str">
         <f aca="false">CONCATENATE(B65,"-",C65,"-",H65)</f>
-        <v>package-&gt;common-description-44</v>
+        <v>package-name-46</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C65" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F65" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="H65" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="D65" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F65" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G65" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="H65" s="15" t="n">
-        <v>44</v>
-      </c>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3"/>
-      <c r="R65" s="3"/>
-      <c r="S65" s="3"/>
-      <c r="T65" s="3"/>
-      <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
-      <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="3"/>
-      <c r="AA65" s="3"/>
-    </row>
-    <row r="66" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="66" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="str">
         <f aca="false">CONCATENATE(B66,"-",C66,"-",H66)</f>
-        <v>package-&gt;common-stereotype-45</v>
+        <v>package-owned elements-47</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E66" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F66" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G66" s="17" t="s">
-        <v>50</v>
+        <v>189</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
-      <c r="O66" s="3"/>
-      <c r="P66" s="3"/>
-      <c r="Q66" s="3"/>
-      <c r="R66" s="3"/>
-      <c r="S66" s="3"/>
-      <c r="T66" s="3"/>
-      <c r="U66" s="3"/>
-      <c r="V66" s="3"/>
-      <c r="W66" s="3"/>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="3"/>
-      <c r="AA66" s="3"/>
-    </row>
-    <row r="67" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="82.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="str">
         <f aca="false">CONCATENATE(B67,"-",C67,"-",H67)</f>
-        <v>class-attribute-type-66</v>
+        <v>package-&gt;common-description-44</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>187</v>
+        <v>47</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>44</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" customFormat="false" ht="82.05" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="str">
         <f aca="false">CONCATENATE(B68,"-",C68,"-",H68)</f>
-        <v>class-name-67</v>
+        <v>package-&gt;common-stereotype-45</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>29</v>
+        <v>193</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="F68" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="G68" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="H68" s="21" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
+    </row>
+    <row r="69" customFormat="false" ht="52.2" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="13" t="str">
         <f aca="false">CONCATENATE(B69,"-",C69,"-",H69)</f>
-        <v>connectors-with-same-name-multiplicity-68</v>
+        <v>class-attribute-type-66</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="F69" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="G69" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="H69" s="22" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F69" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="G69" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="str">
         <f aca="false">CONCATENATE(B70,"-",C70,"-",H70)</f>
-        <v>connectors-with-same-name-definition-69</v>
+        <v>class-name-67</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>195</v>
+        <v>30</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E70" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="F70" s="20" t="s">
+      <c r="E70" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="G70" s="20" t="s">
+      <c r="F70" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="H70" s="21" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G70" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="H70" s="24" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="str">
         <f aca="false">CONCATENATE(B71,"-",C71,"-",H71)</f>
-        <v>connectors-with-same-name-definition-70</v>
+        <v>connectors-with-same-name-multiplicity-68</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="E71" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="F71" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="G71" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="H71" s="22" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="G71" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="H71" s="25" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="52.2" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="str">
         <f aca="false">CONCATENATE(B72,"-",C72,"-",H72)</f>
-        <v>class-attributes-with-same-name-definition-71</v>
+        <v>connectors-with-same-name-definition-69</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>200</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E72" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="F72" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="G72" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="H72" s="21" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E72" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="F72" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="G72" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="H72" s="24" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="39.55" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="13" t="str">
         <f aca="false">CONCATENATE(B73,"-",C73,"-",H73)</f>
-        <v>class-attributes-with-same-name-multiplicity-72</v>
+        <v>connectors-with-same-name-definition-70</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>200</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="F73" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="G73" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="H73" s="22" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>35</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="F73" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="G73" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="H73" s="25" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="52.2" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="str">
         <f aca="false">CONCATENATE(B74,"-",C74,"-",H74)</f>
-        <v>class-attributes-with-same-name-data-types-73</v>
+        <v>class-attributes-with-same-name-definition-71</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D74" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E74" s="20" t="s">
+      <c r="E74" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="F74" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="F74" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="G74" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="H74" s="21" t="n">
+      <c r="G74" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="H74" s="24" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="52.2" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="13" t="str">
+        <f aca="false">CONCATENATE(B75,"-",C75,"-",H75)</f>
+        <v>class-attributes-with-same-name-multiplicity-72</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="F75" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="G75" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="H75" s="25" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="52.2" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="10" t="str">
+        <f aca="false">CONCATENATE(B76,"-",C76,"-",H76)</f>
+        <v>class-attributes-with-same-name-data-types-73</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="F76" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="G76" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="H76" s="24" t="n">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-    </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3"/>
@@ -3065,6 +3192,9 @@
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
+      <c r="I77" s="0" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3"/>
@@ -3075,6 +3205,9 @@
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
+      <c r="I78" s="0" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3"/>
@@ -3085,6 +3218,9 @@
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
+      <c r="I79" s="0" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3"/>
@@ -12286,12 +12422,36 @@
       <c r="G999" s="3"/>
       <c r="H999" s="3"/>
     </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1000" s="3"/>
+      <c r="B1000" s="3"/>
+      <c r="C1000" s="3"/>
+      <c r="D1000" s="3"/>
+      <c r="E1000" s="3"/>
+      <c r="F1000" s="3"/>
+      <c r="G1000" s="3"/>
+      <c r="H1000" s="3"/>
+    </row>
+    <row r="1001" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1001" s="3"/>
+      <c r="B1001" s="3"/>
+      <c r="C1001" s="3"/>
+      <c r="D1001" s="3"/>
+      <c r="E1001" s="3"/>
+      <c r="F1001" s="3"/>
+      <c r="G1001" s="3"/>
+      <c r="H1001" s="3"/>
+    </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A7:H74"/>
+  <autoFilter ref="A7:H76">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="name"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="3">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="A2:F2"/>
